--- a/20_Project_Finance/_template_PROJECT_FINANCE.xlsx
+++ b/20_Project_Finance/_template_PROJECT_FINANCE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t xml:space="preserve">[PROJECT] — Project Finance Model</t>
   </si>
@@ -131,7 +131,22 @@
     <t xml:space="preserve">Minimum DSCR covenant</t>
   </si>
   <si>
-    <t xml:space="preserve">Debt sizing: Max debt = PV of CFADS at target DSCR (build amortization schedule per deal to solve precisely)</t>
+    <t xml:space="preserve">Debt interest rate (for sizing PV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt sizing (sculpted to the DSCR covenant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max annual debt service (CFADS / target DSCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PV of max debt service (discounted at debt rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max sculpted debt (sum of PVs of annual capacity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is capacity, not a repayment schedule — a real deal still needs an amortization profile (sculpted or level) that fits within it and keeps DSCR above covenant every period, not just on average</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -156,12 +171,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="0.00%;\(0.00%\);\-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -238,7 +254,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,6 +271,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,7 +329,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -369,6 +391,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,7 +440,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -629,7 +659,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -691,7 +721,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -792,7 +822,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
@@ -950,8 +980,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:G16"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
@@ -1059,8 +1089,78 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="0" t="s">
         <v>35</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <f aca="false">IFERROR(C5/$C$9,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <f aca="false">IFERROR(D5/$C$9,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <f aca="false">IFERROR(E5/$C$9,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <f aca="false">IFERROR(F5/$C$9,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <f aca="false">IFERROR(G5/$C$9,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <f aca="false">IFERROR(C13/(1+$C$10)^1,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <f aca="false">IFERROR(D13/(1+$C$10)^2,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <f aca="false">IFERROR(E13/(1+$C$10)^3,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <f aca="false">IFERROR(F13/(1+$C$10)^4,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <f aca="false">IFERROR(G13/(1+$C$10)^5,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <f aca="false">SUM(C14:G14)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1080,7 +1180,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1091,95 +1191,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/20_Project_Finance/_template_PROJECT_FINANCE.xlsx
+++ b/20_Project_Finance/_template_PROJECT_FINANCE.xlsx
@@ -1,129 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Construction" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources &amp; Uses" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Operations" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Debt Sculpting" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="DSRA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Coverage" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Checks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sources" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Construction" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Sculpting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSRA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
     <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
     <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.00%;[RED]\(0.00%\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
+    <numFmt numFmtId="166" formatCode="0.00%;[Red](0.00%);-"/>
+    <numFmt numFmtId="167" formatCode="0.0x;[Red](0.0x);-"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF111827"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,14 +117,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,22 +145,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
@@ -201,341 +160,190 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -543,294 +351,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="36" customWidth="1" style="31" min="2" max="2"/>
-    <col width="46" customWidth="1" style="31" min="3" max="3"/>
-    <col width="12" customWidth="1" style="31" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[PROJECT] — Project Finance Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Project / concession:</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[Name]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Sector / jurisdiction:</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Power / transport / digital / PPP</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Financial close / COD:</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>[dates]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="34" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Weekly construction; monthly operations</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$ in millions unless noted</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="36" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="37" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="32">
-      <c r="B16" s="39" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="32">
-      <c r="B17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -842,373 +760,379 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="36" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Debt Service Reserve Account</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 8</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Year 9</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Year 10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Forward debt service</t>
         </is>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="22">
         <f>'Debt Sculpting'!D10</f>
         <v/>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="22">
         <f>'Debt Sculpting'!E10</f>
         <v/>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="22">
         <f>'Debt Sculpting'!F10</f>
         <v/>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="22">
         <f>'Debt Sculpting'!G10</f>
         <v/>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="22">
         <f>'Debt Sculpting'!H10</f>
         <v/>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="22">
         <f>'Debt Sculpting'!I10</f>
         <v/>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="22">
         <f>'Debt Sculpting'!J10</f>
         <v/>
       </c>
-      <c r="J5" s="59">
+      <c r="J5" s="22">
         <f>'Debt Sculpting'!K10</f>
         <v/>
       </c>
-      <c r="K5" s="59">
+      <c r="K5" s="22">
         <f>'Debt Sculpting'!L10</f>
         <v/>
       </c>
-      <c r="L5" s="59">
+      <c r="L5" s="22">
         <f>'Debt Sculpting'!L10</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Required DSRA</t>
         </is>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="22">
         <f>C5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="22">
         <f>D5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="22">
         <f>E5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>F5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="22">
         <f>G5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="22">
         <f>H5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="22">
         <f>I5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="22">
         <f>J5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="22">
         <f>K5*Assumptions!$E$20/12</f>
         <v/>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="22">
         <f>L5*Assumptions!$E$20/12</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Beginning DSRA</t>
         </is>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="22">
         <f>C6</f>
         <v/>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="22">
         <f>C9</f>
         <v/>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="22">
         <f>D9</f>
         <v/>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="22">
         <f>E9</f>
         <v/>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="22">
         <f>F9</f>
         <v/>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="22">
         <f>G9</f>
         <v/>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="22">
         <f>H9</f>
         <v/>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="22">
         <f>I9</f>
         <v/>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="22">
         <f>J9</f>
         <v/>
       </c>
-      <c r="L7" s="59">
+      <c r="L7" s="22">
         <f>K9</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Funding / (release)</t>
         </is>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="22">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="22">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="22">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="22">
         <f>F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="22">
         <f>G6-G7</f>
         <v/>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="22">
         <f>H6-H7</f>
         <v/>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="22">
         <f>I6-I7</f>
         <v/>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="22">
         <f>J6-J7</f>
         <v/>
       </c>
-      <c r="K8" s="59">
+      <c r="K8" s="22">
         <f>K6-K7</f>
         <v/>
       </c>
-      <c r="L8" s="59">
+      <c r="L8" s="22">
         <f>L6-L7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Ending DSRA</t>
         </is>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="22">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="22">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="22">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="22">
         <f>F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="22">
         <f>G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="22">
         <f>H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="22">
         <f>I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="22">
         <f>J7+J8</f>
         <v/>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="22">
         <f>K7+K8</f>
         <v/>
       </c>
-      <c r="L9" s="59">
+      <c r="L9" s="22">
         <f>L7+L8</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DSRA funding at close</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="22">
         <f>IF(COLUMN()=3,C7,0)</f>
         <v/>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="22">
         <f>IF(COLUMN()=3,D7,0)</f>
         <v/>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="22">
         <f>IF(COLUMN()=3,E7,0)</f>
         <v/>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="22">
         <f>IF(COLUMN()=3,F7,0)</f>
         <v/>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="22">
         <f>IF(COLUMN()=3,G7,0)</f>
         <v/>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="22">
         <f>IF(COLUMN()=3,H7,0)</f>
         <v/>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="22">
         <f>IF(COLUMN()=3,I7,0)</f>
         <v/>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="22">
         <f>IF(COLUMN()=3,J7,0)</f>
         <v/>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="22">
         <f>IF(COLUMN()=3,K7,0)</f>
         <v/>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="22">
         <f>IF(COLUMN()=3,L7,0)</f>
         <v/>
       </c>
@@ -1217,462 +1141,469 @@
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="32" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Coverage, Liquidity, and Tail Risk</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 8</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Year 9</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Year 10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="25">
         <f>'Debt Sculpting'!C12</f>
         <v/>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="25">
         <f>'Debt Sculpting'!D12</f>
         <v/>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="25">
         <f>'Debt Sculpting'!E12</f>
         <v/>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="25">
         <f>'Debt Sculpting'!F12</f>
         <v/>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="25">
         <f>'Debt Sculpting'!G12</f>
         <v/>
       </c>
-      <c r="H5" s="62">
+      <c r="H5" s="25">
         <f>'Debt Sculpting'!H12</f>
         <v/>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="25">
         <f>'Debt Sculpting'!I12</f>
         <v/>
       </c>
-      <c r="J5" s="62">
+      <c r="J5" s="25">
         <f>'Debt Sculpting'!J12</f>
         <v/>
       </c>
-      <c r="K5" s="62">
+      <c r="K5" s="25">
         <f>'Debt Sculpting'!K12</f>
         <v/>
       </c>
-      <c r="L5" s="62">
+      <c r="L5" s="25">
         <f>'Debt Sculpting'!L12</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Minimum DSCR</t>
         </is>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="25">
         <f>Assumptions!$E$17</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>DSCR headroom</t>
         </is>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="25">
         <f>C5-C6</f>
         <v/>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="25">
         <f>D5-D6</f>
         <v/>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="25">
         <f>E5-E6</f>
         <v/>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="25">
         <f>F5-F6</f>
         <v/>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="25">
         <f>G5-G6</f>
         <v/>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="25">
         <f>H5-H6</f>
         <v/>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="25">
         <f>I5-I6</f>
         <v/>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="25">
         <f>J5-J6</f>
         <v/>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="25">
         <f>K5-K6</f>
         <v/>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="25">
         <f>L5-L6</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>LLCR</t>
         </is>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="25">
         <f>'Debt Sculpting'!C15</f>
         <v/>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="25">
         <f>'Debt Sculpting'!D15</f>
         <v/>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="25">
         <f>'Debt Sculpting'!E15</f>
         <v/>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="25">
         <f>'Debt Sculpting'!F15</f>
         <v/>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="25">
         <f>'Debt Sculpting'!G15</f>
         <v/>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="25">
         <f>'Debt Sculpting'!H15</f>
         <v/>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="25">
         <f>'Debt Sculpting'!I15</f>
         <v/>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="25">
         <f>'Debt Sculpting'!J15</f>
         <v/>
       </c>
-      <c r="K8" s="62">
+      <c r="K8" s="25">
         <f>'Debt Sculpting'!K15</f>
         <v/>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="25">
         <f>'Debt Sculpting'!L15</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>PLCR</t>
         </is>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!C14:$L$14)/'Debt Sculpting'!C5,0)</f>
         <v/>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!D14:$L$14)/'Debt Sculpting'!D5,0)</f>
         <v/>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!E14:$L$14)/'Debt Sculpting'!E5,0)</f>
         <v/>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!F14:$L$14)/'Debt Sculpting'!F5,0)</f>
         <v/>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!G14:$L$14)/'Debt Sculpting'!G5,0)</f>
         <v/>
       </c>
-      <c r="H9" s="62">
+      <c r="H9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!H14:$L$14)/'Debt Sculpting'!H5,0)</f>
         <v/>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!I14:$L$14)/'Debt Sculpting'!I5,0)</f>
         <v/>
       </c>
-      <c r="J9" s="62">
+      <c r="J9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!J14:$L$14)/'Debt Sculpting'!J5,0)</f>
         <v/>
       </c>
-      <c r="K9" s="62">
+      <c r="K9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!K14:$L$14)/'Debt Sculpting'!K5,0)</f>
         <v/>
       </c>
-      <c r="L9" s="62">
+      <c r="L9" s="25">
         <f>IFERROR(SUM('Debt Sculpting'!L14:$L$14)/'Debt Sculpting'!L5,0)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Debt / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="25">
         <f>IFERROR('Debt Sculpting'!C9/Operations!C8,0)</f>
         <v/>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="25">
         <f>IFERROR('Debt Sculpting'!D9/Operations!D8,0)</f>
         <v/>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="25">
         <f>IFERROR('Debt Sculpting'!E9/Operations!E8,0)</f>
         <v/>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="25">
         <f>IFERROR('Debt Sculpting'!F9/Operations!F8,0)</f>
         <v/>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="25">
         <f>IFERROR('Debt Sculpting'!G9/Operations!G8,0)</f>
         <v/>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="25">
         <f>IFERROR('Debt Sculpting'!H9/Operations!H8,0)</f>
         <v/>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="25">
         <f>IFERROR('Debt Sculpting'!I9/Operations!I8,0)</f>
         <v/>
       </c>
-      <c r="J10" s="62">
+      <c r="J10" s="25">
         <f>IFERROR('Debt Sculpting'!J9/Operations!J8,0)</f>
         <v/>
       </c>
-      <c r="K10" s="62">
+      <c r="K10" s="25">
         <f>IFERROR('Debt Sculpting'!K9/Operations!K8,0)</f>
         <v/>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="25">
         <f>IFERROR('Debt Sculpting'!L9/Operations!L8,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>DSRA coverage</t>
         </is>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="25">
         <f>IFERROR(DSRA!C9/DSRA!C6,0)</f>
         <v/>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="25">
         <f>IFERROR(DSRA!D9/DSRA!D6,0)</f>
         <v/>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="25">
         <f>IFERROR(DSRA!E9/DSRA!E6,0)</f>
         <v/>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="25">
         <f>IFERROR(DSRA!F9/DSRA!F6,0)</f>
         <v/>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="25">
         <f>IFERROR(DSRA!G9/DSRA!G6,0)</f>
         <v/>
       </c>
-      <c r="H11" s="62">
+      <c r="H11" s="25">
         <f>IFERROR(DSRA!H9/DSRA!H6,0)</f>
         <v/>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="25">
         <f>IFERROR(DSRA!I9/DSRA!I6,0)</f>
         <v/>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="25">
         <f>IFERROR(DSRA!J9/DSRA!J6,0)</f>
         <v/>
       </c>
-      <c r="K11" s="62">
+      <c r="K11" s="25">
         <f>IFERROR(DSRA!K9/DSRA!K6,0)</f>
         <v/>
       </c>
-      <c r="L11" s="62">
+      <c r="L11" s="25">
         <f>IFERROR(DSRA!L9/DSRA!L6,0)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Covenant status</t>
         </is>
       </c>
-      <c r="C12" s="31">
+      <c r="C12">
         <f>IF(AND(C7&gt;=0,C8&gt;=1,C11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12">
         <f>IF(AND(D7&gt;=0,D8&gt;=1,D11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12">
         <f>IF(AND(E7&gt;=0,E8&gt;=1,E11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12">
         <f>IF(AND(F7&gt;=0,F8&gt;=1,F11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12">
         <f>IF(AND(G7&gt;=0,G8&gt;=1,G11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12">
         <f>IF(AND(H7&gt;=0,H8&gt;=1,H11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12">
         <f>IF(AND(I7&gt;=0,I8&gt;=1,I11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="J12" s="31">
+      <c r="J12">
         <f>IF(AND(J7&gt;=0,J8&gt;=1,J11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="K12" s="31">
+      <c r="K12">
         <f>IF(AND(K7&gt;=0,K8&gt;=1,K11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="L12" s="31">
+      <c r="L12">
         <f>IF(AND(L7&gt;=0,L8&gt;=1,L11&gt;=1),"PASS","BREACH")</f>
         <v/>
       </c>
@@ -1682,189 +1613,191 @@
     <mergeCell ref="B2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:L12">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C12="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C12="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C12="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C12="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="34" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Minimum DSCR Sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Revenue haircut / Operating cost</t>
         </is>
       </c>
-      <c r="C4" s="64" t="n">
+      <c r="C4" s="27" t="n">
         <v>0.22</v>
       </c>
-      <c r="D4" s="64" t="n">
+      <c r="D4" s="27" t="n">
         <v>0.28</v>
       </c>
-      <c r="E4" s="64" t="n">
+      <c r="E4" s="27" t="n">
         <v>0.34</v>
       </c>
-      <c r="F4" s="64" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="G4" s="64" t="n">
+      <c r="G4" s="27" t="n">
         <v>0.46</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="58" t="n">
+    <row r="5">
+      <c r="B5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B5)*(1-C$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B5)*(1-C$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B5)*(1-C$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B5)*(1-C$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B5)*(1-C$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B5)*(1-C$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B5)*(1-C$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B5)*(1-C$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B5)*(1-C$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B5)*(1-C$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B5)*(1-D$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B5)*(1-D$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B5)*(1-D$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B5)*(1-D$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B5)*(1-D$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B5)*(1-D$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B5)*(1-D$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B5)*(1-D$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B5)*(1-D$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B5)*(1-D$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B5)*(1-E$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B5)*(1-E$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B5)*(1-E$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B5)*(1-E$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B5)*(1-E$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B5)*(1-E$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B5)*(1-E$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B5)*(1-E$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B5)*(1-E$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B5)*(1-E$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B5)*(1-F$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B5)*(1-F$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B5)*(1-F$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B5)*(1-F$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B5)*(1-F$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B5)*(1-F$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B5)*(1-F$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B5)*(1-F$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B5)*(1-F$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B5)*(1-F$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B5)*(1-G$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B5)*(1-G$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B5)*(1-G$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B5)*(1-G$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B5)*(1-G$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B5)*(1-G$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B5)*(1-G$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B5)*(1-G$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B5)*(1-G$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B5)*(1-G$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="58" t="n">
+    <row r="6">
+      <c r="B6" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B6)*(1-C$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B6)*(1-C$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B6)*(1-C$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B6)*(1-C$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B6)*(1-C$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B6)*(1-C$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B6)*(1-C$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B6)*(1-C$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B6)*(1-C$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B6)*(1-C$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B6)*(1-D$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B6)*(1-D$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B6)*(1-D$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B6)*(1-D$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B6)*(1-D$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B6)*(1-D$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B6)*(1-D$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B6)*(1-D$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B6)*(1-D$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B6)*(1-D$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B6)*(1-E$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B6)*(1-E$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B6)*(1-E$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B6)*(1-E$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B6)*(1-E$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B6)*(1-E$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B6)*(1-E$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B6)*(1-E$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B6)*(1-E$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B6)*(1-E$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B6)*(1-F$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B6)*(1-F$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B6)*(1-F$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B6)*(1-F$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B6)*(1-F$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B6)*(1-F$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B6)*(1-F$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B6)*(1-F$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B6)*(1-F$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B6)*(1-F$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B6)*(1-G$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B6)*(1-G$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B6)*(1-G$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B6)*(1-G$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B6)*(1-G$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B6)*(1-G$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B6)*(1-G$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B6)*(1-G$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B6)*(1-G$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B6)*(1-G$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="58" t="n">
+    <row r="7">
+      <c r="B7" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B7)*(1-C$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B7)*(1-C$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B7)*(1-C$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B7)*(1-C$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B7)*(1-C$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B7)*(1-C$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B7)*(1-C$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B7)*(1-C$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B7)*(1-C$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B7)*(1-C$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B7)*(1-D$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B7)*(1-D$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B7)*(1-D$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B7)*(1-D$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B7)*(1-D$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B7)*(1-D$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B7)*(1-D$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B7)*(1-D$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B7)*(1-D$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B7)*(1-D$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B7)*(1-E$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B7)*(1-E$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B7)*(1-E$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B7)*(1-E$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B7)*(1-E$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B7)*(1-E$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B7)*(1-E$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B7)*(1-E$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B7)*(1-E$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B7)*(1-E$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B7)*(1-F$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B7)*(1-F$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B7)*(1-F$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B7)*(1-F$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B7)*(1-F$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B7)*(1-F$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B7)*(1-F$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B7)*(1-F$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B7)*(1-F$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B7)*(1-F$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B7)*(1-G$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B7)*(1-G$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B7)*(1-G$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B7)*(1-G$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B7)*(1-G$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B7)*(1-G$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B7)*(1-G$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B7)*(1-G$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B7)*(1-G$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B7)*(1-G$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="58" t="n">
+    <row r="8">
+      <c r="B8" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B8)*(1-C$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B8)*(1-C$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B8)*(1-C$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B8)*(1-C$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B8)*(1-C$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B8)*(1-C$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B8)*(1-C$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B8)*(1-C$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B8)*(1-C$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B8)*(1-C$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B8)*(1-D$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B8)*(1-D$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B8)*(1-D$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B8)*(1-D$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B8)*(1-D$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B8)*(1-D$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B8)*(1-D$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B8)*(1-D$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B8)*(1-D$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B8)*(1-D$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B8)*(1-E$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B8)*(1-E$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B8)*(1-E$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B8)*(1-E$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B8)*(1-E$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B8)*(1-E$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B8)*(1-E$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B8)*(1-E$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B8)*(1-E$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B8)*(1-E$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B8)*(1-F$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B8)*(1-F$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B8)*(1-F$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B8)*(1-F$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B8)*(1-F$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B8)*(1-F$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B8)*(1-F$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B8)*(1-F$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B8)*(1-F$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B8)*(1-F$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B8)*(1-G$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B8)*(1-G$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B8)*(1-G$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B8)*(1-G$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B8)*(1-G$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B8)*(1-G$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B8)*(1-G$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B8)*(1-G$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B8)*(1-G$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B8)*(1-G$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="58" t="n">
+    <row r="9">
+      <c r="B9" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B9)*(1-C$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B9)*(1-C$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B9)*(1-C$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B9)*(1-C$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B9)*(1-C$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B9)*(1-C$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B9)*(1-C$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B9)*(1-C$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B9)*(1-C$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B9)*(1-C$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B9)*(1-D$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B9)*(1-D$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B9)*(1-D$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B9)*(1-D$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B9)*(1-D$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B9)*(1-D$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B9)*(1-D$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B9)*(1-D$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B9)*(1-D$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B9)*(1-D$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B9)*(1-E$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B9)*(1-E$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B9)*(1-E$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B9)*(1-E$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B9)*(1-E$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B9)*(1-E$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B9)*(1-E$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B9)*(1-E$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B9)*(1-E$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B9)*(1-E$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B9)*(1-F$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B9)*(1-F$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B9)*(1-F$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B9)*(1-F$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B9)*(1-F$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B9)*(1-F$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B9)*(1-F$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B9)*(1-F$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B9)*(1-F$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B9)*(1-F$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="25">
         <f>MIN(MAX(0,Operations!C5*(1-$B9)*(1-G$4)-Operations!C9-Operations!C10-Operations!C11)/MAX(0.000001,'Debt Sculpting'!C10),MAX(0,Operations!D5*(1-$B9)*(1-G$4)-Operations!D9-Operations!D10-Operations!D11)/MAX(0.000001,'Debt Sculpting'!D10),MAX(0,Operations!E5*(1-$B9)*(1-G$4)-Operations!E9-Operations!E10-Operations!E11)/MAX(0.000001,'Debt Sculpting'!E10),MAX(0,Operations!F5*(1-$B9)*(1-G$4)-Operations!F9-Operations!F10-Operations!F11)/MAX(0.000001,'Debt Sculpting'!F10),MAX(0,Operations!G5*(1-$B9)*(1-G$4)-Operations!G9-Operations!G10-Operations!G11)/MAX(0.000001,'Debt Sculpting'!G10),MAX(0,Operations!H5*(1-$B9)*(1-G$4)-Operations!H9-Operations!H10-Operations!H11)/MAX(0.000001,'Debt Sculpting'!H10),MAX(0,Operations!I5*(1-$B9)*(1-G$4)-Operations!I9-Operations!I10-Operations!I11)/MAX(0.000001,'Debt Sculpting'!I10),MAX(0,Operations!J5*(1-$B9)*(1-G$4)-Operations!J9-Operations!J10-Operations!J11)/MAX(0.000001,'Debt Sculpting'!J10),MAX(0,Operations!K5*(1-$B9)*(1-G$4)-Operations!K9-Operations!K10-Operations!K11)/MAX(0.000001,'Debt Sculpting'!K10),MAX(0,Operations!L5*(1-$B9)*(1-G$4)-Operations!L9-Operations!L10-Operations!L11)/MAX(0.000001,'Debt Sculpting'!L10))</f>
         <v/>
       </c>
@@ -1874,140 +1807,138 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
+        <cfvo type="max"/>
+        <color rgb="00FCE4D6"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00E2F0D9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="46" customWidth="1" style="31" min="2" max="2"/>
-    <col width="18" customWidth="1" style="31" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Construction spend curve totals 100%</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5">
         <f>IF(ABS(Construction!M5-1)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Sources equal uses</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6">
         <f>IF(ABS('Sources &amp; Uses'!F9)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Debt never negative</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7">
         <f>IF(MIN('Debt Sculpting'!C9:L9)&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>No DSCR covenant breach</t>
         </is>
       </c>
-      <c r="C8" s="31">
+      <c r="C8">
         <f>IF(MIN(Coverage!C7:L7)&gt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>DSRA fully funded</t>
         </is>
       </c>
-      <c r="C9" s="31">
+      <c r="C9">
         <f>IF(MIN(Coverage!C11:L11)&gt;=1,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>LLCR positive</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10">
         <f>IF(MIN(Coverage!C8:L8)&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Debt repaid or balloon disclosed</t>
         </is>
       </c>
-      <c r="C11" s="31">
+      <c r="C11">
         <f>IF('Debt Sculpting'!L9&lt;0.000001,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Overall model status</t>
         </is>
       </c>
-      <c r="C12" s="31">
+      <c r="C12">
         <f>IF(COUNTIF(C5:C11,"FAIL")=0,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -2017,197 +1948,195 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C12">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="34" customWidth="1" style="31" min="2" max="2"/>
-    <col width="58" customWidth="1" style="31" min="3" max="3"/>
-    <col width="16" customWidth="1" style="31" min="4" max="4"/>
-    <col width="48" customWidth="1" style="31" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="65" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>EPC and construction budget</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>[data room / contract URL]</t>
         </is>
       </c>
-      <c r="D5" s="65" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E5" s="65" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Cost, timing, contingency, liquidated damages</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="65" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Concession / offtake agreement</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>[public filing / contract URL]</t>
         </is>
       </c>
-      <c r="D6" s="65" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E6" s="65" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Tariff, availability, escalation, termination</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="65" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Debt term sheet and common terms</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>[data room URL]</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>Rates, tenor, sculpting, covenants, reserves</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="65" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Independent engineer report</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>[advisor URL]</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Construction and operating assumptions</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="65" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Market / resource study</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>[consultant or public source]</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>Demand, irradiation, wind, traffic, throughput</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="65" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Discount and benchmark rates</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates</t>
         </is>
       </c>
-      <c r="D10" s="65" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Document currency and tenor mapping</t>
         </is>
@@ -2217,276 +2146,272 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="14" customWidth="1" style="31" min="2" max="2"/>
-    <col width="22" customWidth="1" style="31" min="3" max="3"/>
-    <col width="28" customWidth="1" style="31" min="4" max="4"/>
-    <col width="38" customWidth="1" style="31" min="5" max="5"/>
-    <col width="34" customWidth="1" style="31" min="6" max="6"/>
-    <col width="18" customWidth="1" style="31" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="66" t="n"/>
-      <c r="C5" s="66" t="n"/>
-      <c r="D5" s="66" t="n"/>
-      <c r="E5" s="66" t="n"/>
-      <c r="F5" s="66" t="n"/>
-      <c r="G5" s="66" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="66" t="n"/>
-      <c r="C6" s="66" t="n"/>
-      <c r="D6" s="66" t="n"/>
-      <c r="E6" s="66" t="n"/>
-      <c r="F6" s="66" t="n"/>
-      <c r="G6" s="66" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="66" t="n"/>
-      <c r="C7" s="66" t="n"/>
-      <c r="D7" s="66" t="n"/>
-      <c r="E7" s="66" t="n"/>
-      <c r="F7" s="66" t="n"/>
-      <c r="G7" s="66" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="66" t="n"/>
-      <c r="C8" s="66" t="n"/>
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="66" t="n"/>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="66" t="n"/>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="66" t="n"/>
-      <c r="G9" s="66" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="66" t="n"/>
-      <c r="C11" s="66" t="n"/>
-      <c r="D11" s="66" t="n"/>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="66" t="n"/>
-      <c r="G11" s="66" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="66" t="n"/>
-      <c r="C12" s="66" t="n"/>
-      <c r="D12" s="66" t="n"/>
-      <c r="E12" s="66" t="n"/>
-      <c r="F12" s="66" t="n"/>
-      <c r="G12" s="66" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="66" t="n"/>
-      <c r="C13" s="66" t="n"/>
-      <c r="D13" s="66" t="n"/>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="66" t="n"/>
-      <c r="G13" s="66" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="66" t="n"/>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="66" t="n"/>
-      <c r="E15" s="66" t="n"/>
-      <c r="F15" s="66" t="n"/>
-      <c r="G15" s="66" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="32">
-      <c r="B16" s="66" t="n"/>
-      <c r="C16" s="66" t="n"/>
-      <c r="D16" s="66" t="n"/>
-      <c r="E16" s="66" t="n"/>
-      <c r="F16" s="66" t="n"/>
-      <c r="G16" s="66" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="32">
-      <c r="B17" s="66" t="n"/>
-      <c r="C17" s="66" t="n"/>
-      <c r="D17" s="66" t="n"/>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="66" t="n"/>
-      <c r="G17" s="66" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="32">
-      <c r="B18" s="66" t="n"/>
-      <c r="C18" s="66" t="n"/>
-      <c r="D18" s="66" t="n"/>
-      <c r="E18" s="66" t="n"/>
-      <c r="F18" s="66" t="n"/>
-      <c r="G18" s="66" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="32">
-      <c r="B19" s="66" t="n"/>
-      <c r="C19" s="66" t="n"/>
-      <c r="D19" s="66" t="n"/>
-      <c r="E19" s="66" t="n"/>
-      <c r="F19" s="66" t="n"/>
-      <c r="G19" s="66" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="32">
-      <c r="B20" s="66" t="n"/>
-      <c r="C20" s="66" t="n"/>
-      <c r="D20" s="66" t="n"/>
-      <c r="E20" s="66" t="n"/>
-      <c r="F20" s="66" t="n"/>
-      <c r="G20" s="66" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="32">
-      <c r="B21" s="66" t="n"/>
-      <c r="C21" s="66" t="n"/>
-      <c r="D21" s="66" t="n"/>
-      <c r="E21" s="66" t="n"/>
-      <c r="F21" s="66" t="n"/>
-      <c r="G21" s="66" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="32">
-      <c r="B22" s="66" t="n"/>
-      <c r="C22" s="66" t="n"/>
-      <c r="D22" s="66" t="n"/>
-      <c r="E22" s="66" t="n"/>
-      <c r="F22" s="66" t="n"/>
-      <c r="G22" s="66" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="32">
-      <c r="B23" s="66" t="n"/>
-      <c r="C23" s="66" t="n"/>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="66" t="n"/>
-      <c r="F23" s="66" t="n"/>
-      <c r="G23" s="66" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="32">
-      <c r="B24" s="66" t="n"/>
-      <c r="C24" s="66" t="n"/>
-      <c r="D24" s="66" t="n"/>
-      <c r="E24" s="66" t="n"/>
-      <c r="F24" s="66" t="n"/>
-      <c r="G24" s="66" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="32">
-      <c r="B25" s="66" t="n"/>
-      <c r="C25" s="66" t="n"/>
-      <c r="D25" s="66" t="n"/>
-      <c r="E25" s="66" t="n"/>
-      <c r="F25" s="66" t="n"/>
-      <c r="G25" s="66" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="32">
-      <c r="B26" s="66" t="n"/>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="66" t="n"/>
-      <c r="E26" s="66" t="n"/>
-      <c r="F26" s="66" t="n"/>
-      <c r="G26" s="66" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="32">
-      <c r="B27" s="66" t="n"/>
-      <c r="C27" s="66" t="n"/>
-      <c r="D27" s="66" t="n"/>
-      <c r="E27" s="66" t="n"/>
-      <c r="F27" s="66" t="n"/>
-      <c r="G27" s="66" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="32">
-      <c r="B28" s="66" t="n"/>
-      <c r="C28" s="66" t="n"/>
-      <c r="D28" s="66" t="n"/>
-      <c r="E28" s="66" t="n"/>
-      <c r="F28" s="66" t="n"/>
-      <c r="G28" s="66" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="32">
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="66" t="n"/>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
+    <row r="5">
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="29" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2499,133 +2424,133 @@
   <dimension ref="B2:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="32" min="2" max="2"/>
-    <col width="48" customWidth="1" style="32" min="3" max="3"/>
-    <col width="24" customWidth="1" style="32" min="4" max="4"/>
-    <col width="34" customWidth="1" style="32" min="5" max="5"/>
-    <col width="20" customWidth="1" style="32" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Project Finance — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Project Finance</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>tools/builders/build_project_finance_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>sponsor, lender, technical adviser, offtaker, insurer and investment committee</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>bank case, downside case and financing base-case pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>monthly construction/operations; quarterly lender; annual model audit</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="44" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2717,34 +2642,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="44" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="44" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2836,34 +2761,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="44" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="44" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="44" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2955,34 +2880,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="43" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="44" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="44" t="inlineStr">
+      <c r="E37" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="44" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3074,34 +2999,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="43" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="44" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="44" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="44" t="inlineStr">
+      <c r="E45" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="44" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3193,34 +3118,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="43" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="44" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="44" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="44" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="44" t="inlineStr">
+      <c r="E53" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="44" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3312,34 +3237,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="43" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="44" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="44" t="inlineStr">
+      <c r="C61" s="34" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="44" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="44" t="inlineStr">
+      <c r="E61" s="34" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="44" t="inlineStr">
+      <c r="F61" s="34" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3442,60 +3367,60 @@
   <dimension ref="B2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="32" min="2" max="2"/>
-    <col width="22" customWidth="1" style="32" min="3" max="3"/>
-    <col width="52" customWidth="1" style="32" min="4" max="4"/>
-    <col width="46" customWidth="1" style="32" min="5" max="5"/>
-    <col width="36" customWidth="1" style="32" min="6" max="6"/>
-    <col width="14" customWidth="1" style="32" min="7" max="7"/>
-    <col width="18" customWidth="1" style="32" min="8" max="8"/>
-    <col width="14" customWidth="1" style="32" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="44" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3616,66 +3541,66 @@
   <dimension ref="B2:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="32" min="2" max="2"/>
-    <col width="18" customWidth="1" style="32" min="3" max="3"/>
-    <col width="42" customWidth="1" style="32" min="4" max="4"/>
-    <col width="24" customWidth="1" style="32" min="5" max="5"/>
-    <col width="18" customWidth="1" style="32" min="6" max="6"/>
-    <col width="22" customWidth="1" style="32" min="7" max="7"/>
-    <col width="42" customWidth="1" style="32" min="8" max="8"/>
-    <col width="30" customWidth="1" style="32" min="9" max="9"/>
-    <col width="15" customWidth="1" style="32" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="44" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="44" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3804,488 +3729,490 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="46" customWidth="1" style="31" min="2" max="2"/>
-    <col width="15" customWidth="1" style="31" min="3" max="5"/>
-    <col width="32" customWidth="1" style="31" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Project Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Units / note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>EPC / hard construction cost</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n">
+      <c r="C5" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="9" t="n">
         <v>880</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Development and owner costs</t>
         </is>
       </c>
-      <c r="C6" s="46" t="n">
+      <c r="C6" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="10">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Contingency / hard cost</t>
         </is>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="12">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Debt share of pre-IDC cost</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.7</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.65</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="12">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Construction quarters</t>
         </is>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="14">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>quarters</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Annual construction debt rate</t>
         </is>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="15" t="n">
         <v>0.075</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="15" t="n">
         <v>0.09</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="16">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Year 1 contracted / merchant revenue</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="10">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Annual revenue growth</t>
         </is>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="12">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Operating cost / revenue</t>
         </is>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.28</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="11" t="n">
         <v>0.36</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="12">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Maintenance capex / revenue</t>
         </is>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.035</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="12">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="31" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="31" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Cash tax / EBITDA</t>
         </is>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="D15" s="48" t="n">
+      <c r="D15" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="12">
         <f>IF(Cover!$C$9="Downside",D15,C15)</f>
         <v/>
       </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="32">
-      <c r="B16" s="31" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Target DSCR</t>
         </is>
       </c>
-      <c r="C16" s="54" t="n">
+      <c r="C16" s="17" t="n">
         <v>1.35</v>
       </c>
-      <c r="D16" s="54" t="n">
+      <c r="D16" s="17" t="n">
         <v>1.45</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="18">
         <f>IF(Cover!$C$9="Downside",D16,C16)</f>
         <v/>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="32">
-      <c r="B17" s="31" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Minimum DSCR covenant</t>
         </is>
       </c>
-      <c r="C17" s="54" t="n">
+      <c r="C17" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="D17" s="54" t="n">
+      <c r="D17" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="18">
         <f>IF(Cover!$C$9="Downside",D17,C17)</f>
         <v/>
       </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="32">
-      <c r="B18" s="31" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Annual operating debt rate</t>
         </is>
       </c>
-      <c r="C18" s="52" t="n">
+      <c r="C18" s="15" t="n">
         <v>0.065</v>
       </c>
-      <c r="D18" s="52" t="n">
+      <c r="D18" s="15" t="n">
         <v>0.08</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="16">
         <f>IF(Cover!$C$9="Downside",D18,C18)</f>
         <v/>
       </c>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="32">
-      <c r="B19" s="31" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Debt tenor</t>
         </is>
       </c>
-      <c r="C19" s="50" t="n">
+      <c r="C19" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="50" t="n">
+      <c r="D19" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="14">
         <f>IF(Cover!$C$9="Downside",D19,C19)</f>
         <v/>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="32">
-      <c r="B20" s="31" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>DSRA months of forward debt service</t>
         </is>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="D20" s="56" t="n">
+      <c r="D20" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="20">
         <f>IF(Cover!$C$9="Downside",D20,C20)</f>
         <v/>
       </c>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="32">
-      <c r="B21" s="31" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Discount rate for LLCR / PLCR</t>
         </is>
       </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D21" s="52" t="n">
+      <c r="D21" s="15" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="16">
         <f>IF(Cover!$C$9="Downside",D21,C21)</f>
         <v/>
       </c>
-      <c r="F21" s="31" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="32">
-      <c r="B22" s="31" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Residual / decommissioning reserve per year</t>
         </is>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="10">
         <f>IF(Cover!$C$9="Downside",D22,C22)</f>
         <v/>
       </c>
-      <c r="F22" s="31" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="32">
-      <c r="B23" s="31" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Availability / volume factor</t>
         </is>
       </c>
-      <c r="C23" s="48" t="n">
+      <c r="C23" s="11" t="n">
         <v>0.97</v>
       </c>
-      <c r="D23" s="48" t="n">
+      <c r="D23" s="11" t="n">
         <v>0.85</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="12">
         <f>IF(Cover!$C$9="Downside",D23,C23)</f>
         <v/>
       </c>
-      <c r="F23" s="31" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="32">
-      <c r="B24" s="31" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Inflation escalation</t>
         </is>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D24" s="48" t="n">
+      <c r="D24" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="12">
         <f>IF(Cover!$C$9="Downside",D24,C24)</f>
         <v/>
       </c>
-      <c r="F24" s="31" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -4295,641 +4222,649 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="36" customWidth="1" style="31" min="2" max="2"/>
-    <col width="12" customWidth="1" style="31" min="3" max="13"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Quarterly Construction Funding and IDC</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Spend curve</t>
         </is>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="11" t="n">
         <v>0.18</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="11" t="n">
         <v>0.18</v>
       </c>
-      <c r="H5" s="48" t="n">
+      <c r="H5" s="11" t="n">
         <v>0.14</v>
       </c>
-      <c r="I5" s="48" t="n">
+      <c r="I5" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="J5" s="48" t="n">
+      <c r="J5" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="K5" s="48" t="n">
+      <c r="K5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="48" t="n">
+      <c r="L5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="58">
+      <c r="M5" s="21">
         <f>SUM(C5:L5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Hard construction cost</t>
         </is>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="22">
         <f>IF(1&lt;=Assumptions!$E$9,Assumptions!$E$5*C$5,0)</f>
         <v/>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="22">
         <f>IF(2&lt;=Assumptions!$E$9,Assumptions!$E$5*D$5,0)</f>
         <v/>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="22">
         <f>IF(3&lt;=Assumptions!$E$9,Assumptions!$E$5*E$5,0)</f>
         <v/>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>IF(4&lt;=Assumptions!$E$9,Assumptions!$E$5*F$5,0)</f>
         <v/>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="22">
         <f>IF(5&lt;=Assumptions!$E$9,Assumptions!$E$5*G$5,0)</f>
         <v/>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="22">
         <f>IF(6&lt;=Assumptions!$E$9,Assumptions!$E$5*H$5,0)</f>
         <v/>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="22">
         <f>IF(7&lt;=Assumptions!$E$9,Assumptions!$E$5*I$5,0)</f>
         <v/>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="22">
         <f>IF(8&lt;=Assumptions!$E$9,Assumptions!$E$5*J$5,0)</f>
         <v/>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="22">
         <f>IF(9&lt;=Assumptions!$E$9,Assumptions!$E$5*K$5,0)</f>
         <v/>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="22">
         <f>IF(10&lt;=Assumptions!$E$9,Assumptions!$E$5*L$5,0)</f>
         <v/>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="22">
         <f>SUM(C6:L6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Development / owner costs</t>
         </is>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="22">
         <f>IF(1&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="22">
         <f>IF(2&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="22">
         <f>IF(3&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="22">
         <f>IF(4&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="22">
         <f>IF(5&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="22">
         <f>IF(6&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="22">
         <f>IF(7&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="22">
         <f>IF(8&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="22">
         <f>IF(9&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="L7" s="59">
+      <c r="L7" s="22">
         <f>IF(10&lt;=Assumptions!$E$9,Assumptions!$E$6/Assumptions!$E$9,0)</f>
         <v/>
       </c>
-      <c r="M7" s="59">
+      <c r="M7" s="22">
         <f>SUM(C7:L7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="22">
         <f>C6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="22">
         <f>D6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="22">
         <f>E6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="22">
         <f>F6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="22">
         <f>G6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="22">
         <f>H6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="22">
         <f>I6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="22">
         <f>J6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="K8" s="59">
+      <c r="K8" s="22">
         <f>K6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="L8" s="59">
+      <c r="L8" s="22">
         <f>L6*Assumptions!$E$7</f>
         <v/>
       </c>
-      <c r="M8" s="59">
+      <c r="M8" s="22">
         <f>SUM(C8:L8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="60" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Total pre-IDC spend</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="24">
         <f>SUM(C6:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="24">
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="24">
         <f>SUM(E6:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="24">
         <f>SUM(F6:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="24">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="24">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="24">
         <f>SUM(I6:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="24">
         <f>SUM(J6:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="24">
         <f>SUM(K6:K8)</f>
         <v/>
       </c>
-      <c r="L9" s="61">
+      <c r="L9" s="24">
         <f>SUM(L6:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="61">
+      <c r="M9" s="24">
         <f>SUM(C9:L9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Equity draw</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="22">
         <f>C9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="22">
         <f>D9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="22">
         <f>E9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="22">
         <f>F9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="22">
         <f>G9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="22">
         <f>H9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="22">
         <f>I9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="22">
         <f>J9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="22">
         <f>K9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="22">
         <f>L9*(1-Assumptions!$E$8)</f>
         <v/>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="22">
         <f>SUM(C10:L10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Debt draw</t>
         </is>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="22">
         <f>C9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="22">
         <f>D9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="22">
         <f>E9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="22">
         <f>F9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="22">
         <f>G9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="22">
         <f>H9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="22">
         <f>I9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="J11" s="59">
+      <c r="J11" s="22">
         <f>J9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="22">
         <f>K9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="L11" s="59">
+      <c r="L11" s="22">
         <f>L9*Assumptions!$E$8</f>
         <v/>
       </c>
-      <c r="M11" s="59">
+      <c r="M11" s="22">
         <f>SUM(C11:L11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Beginning construction debt</t>
         </is>
       </c>
-      <c r="C12" s="59" t="n">
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="22">
         <f>C14</f>
         <v/>
       </c>
-      <c r="E12" s="59">
+      <c r="E12" s="22">
         <f>D14</f>
         <v/>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="22">
         <f>E14</f>
         <v/>
       </c>
-      <c r="G12" s="59">
+      <c r="G12" s="22">
         <f>F14</f>
         <v/>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="22">
         <f>G14</f>
         <v/>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="22">
         <f>H14</f>
         <v/>
       </c>
-      <c r="J12" s="59">
+      <c r="J12" s="22">
         <f>I14</f>
         <v/>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="22">
         <f>J14</f>
         <v/>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="22">
         <f>K14</f>
         <v/>
       </c>
-      <c r="M12" s="59">
+      <c r="M12" s="22">
         <f>SUM(C12:L12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Interest during construction</t>
         </is>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="22">
         <f>(C12+0.5*C11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="22">
         <f>(D12+0.5*D11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="22">
         <f>(E12+0.5*E11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="22">
         <f>(F12+0.5*F11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="22">
         <f>(G12+0.5*G11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="H13" s="59">
+      <c r="H13" s="22">
         <f>(H12+0.5*H11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="I13" s="59">
+      <c r="I13" s="22">
         <f>(I12+0.5*I11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="J13" s="59">
+      <c r="J13" s="22">
         <f>(J12+0.5*J11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="22">
         <f>(K12+0.5*K11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="L13" s="59">
+      <c r="L13" s="22">
         <f>(L12+0.5*L11)*Assumptions!$E$10/4</f>
         <v/>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="22">
         <f>SUM(C13:L13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="60" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Ending construction debt</t>
         </is>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="24">
         <f>C12+C11+C13</f>
         <v/>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="24">
         <f>D12+D11+D13</f>
         <v/>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="24">
         <f>E12+E11+E13</f>
         <v/>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="24">
         <f>F12+F11+F13</f>
         <v/>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="24">
         <f>G12+G11+G13</f>
         <v/>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="24">
         <f>H12+H11+H13</f>
         <v/>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="24">
         <f>I12+I11+I13</f>
         <v/>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="24">
         <f>J12+J11+J13</f>
         <v/>
       </c>
-      <c r="K14" s="61">
+      <c r="K14" s="24">
         <f>K12+K11+K13</f>
         <v/>
       </c>
-      <c r="L14" s="61">
+      <c r="L14" s="24">
         <f>L12+L11+L13</f>
         <v/>
       </c>
-      <c r="M14" s="61">
+      <c r="M14" s="24">
         <f>L14</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="60" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Cumulative project spend</t>
         </is>
       </c>
-      <c r="C15" s="61">
+      <c r="C15" s="24">
         <f>C9</f>
         <v/>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="24">
         <f>C15+D9</f>
         <v/>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="24">
         <f>D15+E9</f>
         <v/>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="24">
         <f>E15+F9</f>
         <v/>
       </c>
-      <c r="G15" s="61">
+      <c r="G15" s="24">
         <f>F15+G9</f>
         <v/>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="24">
         <f>G15+H9</f>
         <v/>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="24">
         <f>H15+I9</f>
         <v/>
       </c>
-      <c r="J15" s="61">
+      <c r="J15" s="24">
         <f>I15+J9</f>
         <v/>
       </c>
-      <c r="K15" s="61">
+      <c r="K15" s="24">
         <f>J15+K9</f>
         <v/>
       </c>
-      <c r="L15" s="61">
+      <c r="L15" s="24">
         <f>K15+L9</f>
         <v/>
       </c>
-      <c r="M15" s="61">
+      <c r="M15" s="24">
         <f>L15</f>
         <v/>
       </c>
@@ -4938,167 +4873,165 @@
   <mergeCells count="1">
     <mergeCell ref="B2:M2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="34" customWidth="1" style="31" min="2" max="2"/>
-    <col width="18" customWidth="1" style="31" min="3" max="3"/>
-    <col width="5" customWidth="1" style="31" min="4" max="4"/>
-    <col width="34" customWidth="1" style="31" min="5" max="5"/>
-    <col width="18" customWidth="1" style="31" min="6" max="6"/>
-    <col width="5" customWidth="1" style="31" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Sources &amp; Uses at Financial Close</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Uses</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D4" s="45" t="n"/>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G4" s="45" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Hard construction cost</t>
         </is>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="22">
         <f>Construction!M6</f>
         <v/>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Construction / term debt</t>
         </is>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="22">
         <f>Construction!M14</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Development / owner costs</t>
         </is>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="22">
         <f>Construction!M7</f>
         <v/>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Sponsor equity</t>
         </is>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>MAX(0,C10-F5)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="22">
         <f>Construction!M8</f>
         <v/>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Grants / subordinated support</t>
         </is>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Interest during construction</t>
         </is>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="22">
         <f>Construction!M13</f>
         <v/>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Total sources</t>
         </is>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="24">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Initial DSRA funding</t>
         </is>
       </c>
-      <c r="C9" s="59">
-        <f>DSRA!C7</f>
-        <v/>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="C9" s="22">
+        <f>'DSRA'!C7</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Sources less uses</t>
         </is>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="22">
         <f>F8-C10</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="60" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Total uses</t>
         </is>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="24">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
@@ -5107,462 +5040,469 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="42" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Ten-Year Operating Forecast and CFADS</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 8</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Year 9</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Year 10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Nominal contracted / merchant revenue</t>
         </is>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="22">
         <f>Assumptions!E11</f>
         <v/>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="22">
         <f>C5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="22">
         <f>D5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="22">
         <f>E5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="22">
         <f>F5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="22">
         <f>G5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="22">
         <f>H5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="J5" s="59">
+      <c r="J5" s="22">
         <f>I5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="K5" s="59">
+      <c r="K5" s="22">
         <f>J5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
-      <c r="L5" s="59">
+      <c r="L5" s="22">
         <f>K5*(1+Assumptions!$E$12+Assumptions!$E$24)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Availability-adjusted revenue</t>
         </is>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="22">
         <f>C5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="22">
         <f>D5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="22">
         <f>E5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>F5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="22">
         <f>G5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="22">
         <f>H5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="22">
         <f>I5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="22">
         <f>J5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="22">
         <f>K5*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="22">
         <f>L5*Assumptions!$E$23</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Operating cost</t>
         </is>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="22">
         <f>C6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="22">
         <f>D6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="22">
         <f>E6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="22">
         <f>F6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="22">
         <f>G6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="22">
         <f>H6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="22">
         <f>I6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="22">
         <f>J6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="22">
         <f>K6*Assumptions!$E$13</f>
         <v/>
       </c>
-      <c r="L7" s="59">
+      <c r="L7" s="22">
         <f>L6*Assumptions!$E$13</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="60" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="24">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="24">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="24">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="24">
         <f>F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="24">
         <f>G6-G7</f>
         <v/>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="24">
         <f>H6-H7</f>
         <v/>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="24">
         <f>I6-I7</f>
         <v/>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="24">
         <f>J6-J7</f>
         <v/>
       </c>
-      <c r="K8" s="61">
+      <c r="K8" s="24">
         <f>K6-K7</f>
         <v/>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="24">
         <f>L6-L7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cash taxes</t>
         </is>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="22">
         <f>MAX(0,C8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="22">
         <f>MAX(0,D8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="22">
         <f>MAX(0,E8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="22">
         <f>MAX(0,F8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="22">
         <f>MAX(0,G8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="22">
         <f>MAX(0,H8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="22">
         <f>MAX(0,I8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="22">
         <f>MAX(0,J8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="22">
         <f>MAX(0,K8*Assumptions!$E$15)</f>
         <v/>
       </c>
-      <c r="L9" s="59">
+      <c r="L9" s="22">
         <f>MAX(0,L8*Assumptions!$E$15)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Maintenance capex</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="22">
         <f>C6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="22">
         <f>D6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="22">
         <f>E6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="22">
         <f>F6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="22">
         <f>G6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="22">
         <f>H6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="22">
         <f>I6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="22">
         <f>J6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="22">
         <f>K6*Assumptions!$E$14</f>
         <v/>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="22">
         <f>L6*Assumptions!$E$14</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Decommissioning / lifecycle reserve</t>
         </is>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="J11" s="59">
+      <c r="J11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
-      <c r="L11" s="59">
+      <c r="L11" s="22">
         <f>Assumptions!$E$22</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="60" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="24">
         <f>C8-C9-C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="24">
         <f>D8-D9-D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="24">
         <f>E8-E9-E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="24">
         <f>F8-F9-F10-F11</f>
         <v/>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="24">
         <f>G8-G9-G10-G11</f>
         <v/>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="24">
         <f>H8-H9-H10-H11</f>
         <v/>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="24">
         <f>I8-I9-I10-I11</f>
         <v/>
       </c>
-      <c r="J12" s="61">
+      <c r="J12" s="24">
         <f>J8-J9-J10-J11</f>
         <v/>
       </c>
-      <c r="K12" s="61">
+      <c r="K12" s="24">
         <f>K8-K9-K10-K11</f>
         <v/>
       </c>
-      <c r="L12" s="61">
+      <c r="L12" s="24">
         <f>L8-L9-L10-L11</f>
         <v/>
       </c>
@@ -5571,603 +5511,610 @@
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:L15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="44" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Sculpted Term Debt Schedule</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm / x</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 8</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Year 9</t>
         </is>
       </c>
-      <c r="L4" s="45" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Year 10</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Beginning debt</t>
         </is>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="22">
         <f>Construction!M14</f>
         <v/>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="22">
         <f>C9</f>
         <v/>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="22">
         <f>D9</f>
         <v/>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="22">
         <f>E9</f>
         <v/>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="22">
         <f>F9</f>
         <v/>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="22">
         <f>G9</f>
         <v/>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="22">
         <f>H9</f>
         <v/>
       </c>
-      <c r="J5" s="59">
+      <c r="J5" s="22">
         <f>I9</f>
         <v/>
       </c>
-      <c r="K5" s="59">
+      <c r="K5" s="22">
         <f>J9</f>
         <v/>
       </c>
-      <c r="L5" s="59">
+      <c r="L5" s="22">
         <f>K9</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="22">
         <f>C5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="22">
         <f>D5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="22">
         <f>E5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>F5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="22">
         <f>G5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="22">
         <f>H5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="22">
         <f>I5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="22">
         <f>J5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="22">
         <f>K5*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="22">
         <f>L5*Assumptions!$E$18</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Maximum debt service at target DSCR</t>
         </is>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="22">
         <f>Operations!C12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="22">
         <f>Operations!D12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="22">
         <f>Operations!E12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="22">
         <f>Operations!F12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="22">
         <f>Operations!G12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="22">
         <f>Operations!H12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="22">
         <f>Operations!I12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="22">
         <f>Operations!J12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="22">
         <f>Operations!K12/Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="L7" s="59">
+      <c r="L7" s="22">
         <f>Operations!L12/Assumptions!$E$16</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Scheduled principal</t>
         </is>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="22">
         <f>MIN(C5,MAX(0,MAX(0,C7-C6)))</f>
         <v/>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="22">
         <f>MIN(D5,MAX(0,MAX(0,D7-D6)))</f>
         <v/>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="22">
         <f>MIN(E5,MAX(0,MAX(0,E7-E6)))</f>
         <v/>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="22">
         <f>MIN(F5,MAX(0,MAX(0,F7-F6)))</f>
         <v/>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="22">
         <f>MIN(G5,MAX(0,MAX(0,G7-G6)))</f>
         <v/>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="22">
         <f>MIN(H5,MAX(0,MAX(0,H7-H6)))</f>
         <v/>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="22">
         <f>MIN(I5,MAX(0,MAX(0,I7-I6)))</f>
         <v/>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="22">
         <f>MIN(J5,MAX(0,MAX(0,J7-J6)))</f>
         <v/>
       </c>
-      <c r="K8" s="59">
+      <c r="K8" s="22">
         <f>MIN(K5,MAX(0,MAX(0,K7-K6)))</f>
         <v/>
       </c>
-      <c r="L8" s="59">
+      <c r="L8" s="22">
         <f>MIN(L5,MAX(L5,MAX(0,L7-L6)))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="60" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Ending debt</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="24">
         <f>MAX(0,C5-C8)</f>
         <v/>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="24">
         <f>MAX(0,D5-D8)</f>
         <v/>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="24">
         <f>MAX(0,E5-E8)</f>
         <v/>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="24">
         <f>MAX(0,F5-F8)</f>
         <v/>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="24">
         <f>MAX(0,G5-G8)</f>
         <v/>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="24">
         <f>MAX(0,H5-H8)</f>
         <v/>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="24">
         <f>MAX(0,I5-I8)</f>
         <v/>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="24">
         <f>MAX(0,J5-J8)</f>
         <v/>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="24">
         <f>MAX(0,K5-K8)</f>
         <v/>
       </c>
-      <c r="L9" s="61">
+      <c r="L9" s="24">
         <f>MAX(0,L5-L8)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="60" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Actual debt service</t>
         </is>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="24">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="24">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="24">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="24">
         <f>F6+F8</f>
         <v/>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="24">
         <f>G6+G8</f>
         <v/>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="24">
         <f>H6+H8</f>
         <v/>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="24">
         <f>I6+I8</f>
         <v/>
       </c>
-      <c r="J10" s="61">
+      <c r="J10" s="24">
         <f>J6+J8</f>
         <v/>
       </c>
-      <c r="K10" s="61">
+      <c r="K10" s="24">
         <f>K6+K8</f>
         <v/>
       </c>
-      <c r="L10" s="61">
+      <c r="L10" s="24">
         <f>L6+L8</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="22">
         <f>Operations!C12</f>
         <v/>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="22">
         <f>Operations!D12</f>
         <v/>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="22">
         <f>Operations!E12</f>
         <v/>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="22">
         <f>Operations!F12</f>
         <v/>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="22">
         <f>Operations!G12</f>
         <v/>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="22">
         <f>Operations!H12</f>
         <v/>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="22">
         <f>Operations!I12</f>
         <v/>
       </c>
-      <c r="J11" s="59">
+      <c r="J11" s="22">
         <f>Operations!J12</f>
         <v/>
       </c>
-      <c r="K11" s="59">
+      <c r="K11" s="22">
         <f>Operations!K12</f>
         <v/>
       </c>
-      <c r="L11" s="59">
+      <c r="L11" s="22">
         <f>Operations!L12</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="25">
         <f>IFERROR(C11/C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="25">
         <f>IFERROR(D11/D10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="25">
         <f>IFERROR(E11/E10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="25">
         <f>IFERROR(F11/F10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="25">
         <f>IFERROR(G11/G10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="25">
         <f>IFERROR(H11/H10,0)</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="25">
         <f>IFERROR(I11/I10,0)</f>
         <v/>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="25">
         <f>IFERROR(J11/J10,0)</f>
         <v/>
       </c>
-      <c r="K12" s="62">
+      <c r="K12" s="25">
         <f>IFERROR(K11/K10,0)</f>
         <v/>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="25">
         <f>IFERROR(L11/L10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="26">
         <f>1/(1+Assumptions!$E$21)^1</f>
         <v/>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="26">
         <f>1/(1+Assumptions!$E$21)^2</f>
         <v/>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="26">
         <f>1/(1+Assumptions!$E$21)^3</f>
         <v/>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="26">
         <f>1/(1+Assumptions!$E$21)^4</f>
         <v/>
       </c>
-      <c r="G13" s="63">
+      <c r="G13" s="26">
         <f>1/(1+Assumptions!$E$21)^5</f>
         <v/>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="26">
         <f>1/(1+Assumptions!$E$21)^6</f>
         <v/>
       </c>
-      <c r="I13" s="63">
+      <c r="I13" s="26">
         <f>1/(1+Assumptions!$E$21)^7</f>
         <v/>
       </c>
-      <c r="J13" s="63">
+      <c r="J13" s="26">
         <f>1/(1+Assumptions!$E$21)^8</f>
         <v/>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="26">
         <f>1/(1+Assumptions!$E$21)^9</f>
         <v/>
       </c>
-      <c r="L13" s="63">
+      <c r="L13" s="26">
         <f>1/(1+Assumptions!$E$21)^10</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>PV of CFADS</t>
         </is>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="22">
         <f>C11*C13</f>
         <v/>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="22">
         <f>D11*D13</f>
         <v/>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="22">
         <f>E11*E13</f>
         <v/>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="22">
         <f>F11*F13</f>
         <v/>
       </c>
-      <c r="G14" s="59">
+      <c r="G14" s="22">
         <f>G11*G13</f>
         <v/>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="22">
         <f>H11*H13</f>
         <v/>
       </c>
-      <c r="I14" s="59">
+      <c r="I14" s="22">
         <f>I11*I13</f>
         <v/>
       </c>
-      <c r="J14" s="59">
+      <c r="J14" s="22">
         <f>J11*J13</f>
         <v/>
       </c>
-      <c r="K14" s="59">
+      <c r="K14" s="22">
         <f>K11*K13</f>
         <v/>
       </c>
-      <c r="L14" s="59">
+      <c r="L14" s="22">
         <f>L11*L13</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="31" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>LLCR from each year</t>
         </is>
       </c>
-      <c r="C15" s="62">
+      <c r="C15" s="25">
         <f>IFERROR(SUM(C14:$L$14)/C5,0)</f>
         <v/>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="25">
         <f>IFERROR(SUM(D14:$L$14)/D5,0)</f>
         <v/>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="25">
         <f>IFERROR(SUM(E14:$L$14)/E5,0)</f>
         <v/>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="25">
         <f>IFERROR(SUM(F14:$L$14)/F5,0)</f>
         <v/>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="25">
         <f>IFERROR(SUM(G14:$L$14)/G5,0)</f>
         <v/>
       </c>
-      <c r="H15" s="62">
+      <c r="H15" s="25">
         <f>IFERROR(SUM(H14:$L$14)/H5,0)</f>
         <v/>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="25">
         <f>IFERROR(SUM(I14:$L$14)/I5,0)</f>
         <v/>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="25">
         <f>IFERROR(SUM(J14:$L$14)/J5,0)</f>
         <v/>
       </c>
-      <c r="K15" s="62">
+      <c r="K15" s="25">
         <f>IFERROR(SUM(K14:$L$14)/K5,0)</f>
         <v/>
       </c>
-      <c r="L15" s="62">
+      <c r="L15" s="25">
         <f>IFERROR(SUM(L14:$L$14)/L5,0)</f>
         <v/>
       </c>
@@ -6176,8 +6123,6 @@
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>